--- a/demo 4 (alpha interpolated)/Pb210_results/CA modeling data/elogpb210_zi_CA_summary.xlsx
+++ b/demo 4 (alpha interpolated)/Pb210_results/CA modeling data/elogpb210_zi_CA_summary.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.704879073689459</v>
+        <v>2.707221409595259</v>
       </c>
       <c r="D2">
-        <v>0.07331315572157236</v>
+        <v>0.07434820684992466</v>
       </c>
       <c r="E2">
-        <v>36.89486623604105</v>
+        <v>36.41273306106645</v>
       </c>
       <c r="F2">
-        <v>2.080897539194654E-28</v>
+        <v>3.179638391717282E-28</v>
       </c>
       <c r="G2">
-        <v>0.9351634987696421</v>
+        <v>0.9341186514942488</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.08043306395468962</v>
+        <v>-0.08087543219003229</v>
       </c>
       <c r="D3">
-        <v>0.003628430568994299</v>
+        <v>0.003679657543438675</v>
       </c>
       <c r="E3">
-        <v>-22.1674529594164</v>
+        <v>-21.9790649633263</v>
       </c>
       <c r="F3">
-        <v>2.156644552075741E-21</v>
+        <v>2.809037147052122E-21</v>
       </c>
       <c r="G3">
-        <v>0.9351634987696421</v>
+        <v>0.9341186514942488</v>
       </c>
     </row>
   </sheetData>
